--- a/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AXAHY_YR_FIN.xlsx
@@ -2218,10 +2218,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>54956000</v>
+        <v>59248600</v>
       </c>
       <c r="E42" s="3">
-        <v>50579800</v>
+        <v>55464300</v>
       </c>
       <c r="F42" s="3">
         <v>54979600</v>
@@ -2371,10 +2371,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>37708100</v>
+        <v>33415500</v>
       </c>
       <c r="E45" s="3">
-        <v>40887300</v>
+        <v>36002700</v>
       </c>
       <c r="F45" s="3">
         <v>42566600</v>
@@ -2974,10 +2974,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>44793900</v>
+        <v>48411400</v>
       </c>
       <c r="E58" s="3">
-        <v>35226200</v>
+        <v>38642700</v>
       </c>
       <c r="F58" s="3">
         <v>39207500</v>
@@ -3025,10 +3025,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>21231700</v>
+        <v>14332500</v>
       </c>
       <c r="E59" s="3">
-        <v>22452600</v>
+        <v>15730400</v>
       </c>
       <c r="F59" s="3">
         <v>25271400</v>
@@ -3076,10 +3076,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>66177100</v>
+        <v>62895400</v>
       </c>
       <c r="E60" s="3">
-        <v>57777200</v>
+        <v>54471500</v>
       </c>
       <c r="F60" s="3">
         <v>64580500</v>
@@ -3127,10 +3127,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>26056100</v>
+        <v>28704900</v>
       </c>
       <c r="E61" s="3">
-        <v>29107600</v>
+        <v>31972300</v>
       </c>
       <c r="F61" s="3">
         <v>26605500</v>
@@ -3178,10 +3178,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>585458500</v>
+        <v>586091300</v>
       </c>
       <c r="E62" s="3">
-        <v>521780700</v>
+        <v>522221800</v>
       </c>
       <c r="F62" s="3">
         <v>548925600</v>
